--- a/UcuzBilgisayar/WebScrapper/BILGISAYAR_URUNLERI.xlsx
+++ b/UcuzBilgisayar/WebScrapper/BILGISAYAR_URUNLERI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5C3A02D28638C25E/Desktop/ito-bilgisayar-urunleri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_53D540F50A234F1ABE610802856E17AB797854E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{194F7FB8-F228-4B16-9FC3-F3A5626F4D8E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_7309C2F9368B092D02610883D52F35C378783EAB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{451D7188-90AB-4AA5-91DE-9F1A1FAAFFE0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="184">
   <si>
     <t>Ürün adı</t>
   </si>
@@ -37,520 +37,541 @@
     <t>Yorum sayısı</t>
   </si>
   <si>
+    <t>Excalibur E27FVC-E 27" 300HZ 1MS 400NIT Fast VA Curved HDR10 Oyuncu Monitörü</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X5T-5050 C7 Intel Core I5 13500HX 16GB Ram 1tb SSD RTX5050 16" Wuxga 165Hz IPS Freedos Oyuncu Laptop</t>
+  </si>
+  <si>
+    <t>Beyaz Oyuncu Masası 160x60, Bilgisayar Masası, Gamer Masası, Gaming Masa, Metal Ayaklı</t>
+  </si>
+  <si>
+    <t>Lenovo LOQ Essential AMD Ryzen 7 7735HS 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar 83S00033TR</t>
+  </si>
+  <si>
+    <t>MSI KATANA 17 HX B14WFK-217TR Intel Core i9 14900HX 32GB 1TB SSD RTX5060 Windows 11 Home 17.3" QHD 240Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Orion Cube 3x Tuştan Değişen RGB Fanlı M-Atx Boş Bilgisayar Kasası Beyaz</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 AMD Ryzen 7 7735HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K70098TR</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Pastel Pembe  MHFH4TU/A</t>
+  </si>
+  <si>
+    <t>Macbook Air M2 M3 M4 M5 13.6 A3113 A3240 A2681 ile Uyumlu Parlak Simli Şeffaf Kılıf Kapak Koruma</t>
+  </si>
+  <si>
+    <t>IdeaPad Slim3 Intel Core i5-13420H 16GB 512GB SSD 15.3" WUXGA FreeDOS  Dizüstü Bilgisayar 83K1003MTR</t>
+  </si>
+  <si>
+    <t>Yeni 2025 MatePad 11.5" PaperMatte 8GB 256GB Tablet + Klavye</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7535HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K7009ETR</t>
+  </si>
+  <si>
+    <t>HP AI 15 Intel Core Ultra 5 225U 16GB 512GB SSD Freedos 15.6" Taşınabilir Bilgisayar D51E0EA</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 A13UC-2087XTR Intel Core i5 13420H 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Aspire Lite Intel Celeron-N4500 8GB 256GB SSD 15.6" FHD DOS (İşletim Sistemsiz) Laptop NX.J9SEY.001</t>
+  </si>
+  <si>
+    <t>Asus Zenbook S 16 UM5606WA-RK411W AMD Ryzen AI 9 HX 370 32GB 1TB SSD Windows 11 Home 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M4 16GB 256GB SSD macOS 15" Taşınabilir Bilgisayar Gök Mavisi MC7A4TU/A</t>
+  </si>
+  <si>
+    <t>Pg-46-cl-56 | E414-404-484-474 Renkli Orjinal Kartuş Seti</t>
+  </si>
+  <si>
+    <t>Lenovo LOQE AMD Ryzen 7 7735HS 16GB 512GB SSD RTX4050 Freedos 15.6" Taşınabilir Bilgisayar 83S0002YTR</t>
+  </si>
+  <si>
+    <t>Nirvana Intel Celeron N4020 4GB RAM 120GB SSD Windows 11 Home 15.6" Hd Laptop C370.4020-4C00B</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFG4TU/A</t>
+  </si>
+  <si>
+    <t>Ideapad Slim 3 AMD Ryzen 5-7520U 8GB 512GB SSD 15.6" FHD Dizüstü Bilgisayar 82XQ00RWTX</t>
+  </si>
+  <si>
+    <t>Siyah/Beyaz Oyuncu Masası 60x140 Cm, Beyaz Renk Bilgisayar Masası, Gamer Masası, Gaming Masa</t>
+  </si>
+  <si>
+    <t>ASUS TUF Gaming F16 FX608JMR-RV075 Intel Core i7 14650HX 16GB 1TB SSD RTX5060 Freedos 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
     <t>LOQE AMD Ryzen 7-7735HS 16GB 512GB SSD 15.6" FHD 144Hz RTX4050 6GB FreeDOS Gaming Laptop 83S0002YTR</t>
   </si>
   <si>
+    <t>Apple Macbook Air 13.6 M2 M3 M4 M5 A2681 A3113 A3240 A3449 Kristal Kılıf Şeffaf Tam Koruma Kapak</t>
+  </si>
+  <si>
+    <t>Ideapad Slim 3 Intel N100 4gb Ram 128GB Ssd 15.6'' 82XB009GTX</t>
+  </si>
+  <si>
+    <t>Victus 15-FA2051NT Intel Core i5-14450HX 24G 1TB SSD RTX4050 6GB Freedos 15.6" FHD IPS 144Hz D2QG6EA</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M4 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gece Yarısı MW133TU/A</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gök Mavisi MDHH4TU/A</t>
+  </si>
+  <si>
+    <t>13" MacBook Neo Pastel Pembe 256GB</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 15" Taşınabilir Bilgisayar Gece Yarısı MDVH4TU/A</t>
+  </si>
+  <si>
+    <t>Pro MP275W E2 27" 120Hz 1ms FHD Flat IPS Adaptive-Sync Monitör</t>
+  </si>
+  <si>
+    <t>Lenovo Case 15.6" Toploader T210 Taşınabilir Bilgisayar Çantası Siyah GX40Q17229</t>
+  </si>
+  <si>
+    <t>Asus Tuf Gaming F16 FX608JMR-RV078 Intel Core I7 14650HX 32GB 1 Tb SSD RTX5060-8GB 115W Freedos 16" 165Hz Wuxga Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Hp Prelude 15.6" Bilgisayar Çantası Gri 2Z8P4AA</t>
+  </si>
+  <si>
+    <t>Triline Nb F160+FP Gazlı Çift Kol Monitör Standı 17-30" Ekran ve 10-17" Dizüstü Bilgisayar İçin Metal</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 Intel Core i5 13420H 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K1003MTR</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5070 C2 Intel Core i7 14650HX 32GB 1TB SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFF4TU/A</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 Intel N100 8GB 128GB SSD Windows 11 Home 15.6" FHD Taşınabilir Bilgisayar 82XB00HMTX</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 B13WFKG-495XTR Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFC4TU/A</t>
+  </si>
+  <si>
+    <t>Casper Excalibur G915 Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 16" 165Hz Taşınabilir Bilgisayar G915.1362-DF60X-C</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5060 C2 Intel Core I7 14650HX 32GB Ram 1tb SSD RTX5060 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFA4TU/A</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5070 C7 Intel Core I7 14650HX 16GB Ram 1tb SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
+    <t>Asus Tuf Gaming A16 FA608UM-RV130 Amd Ryzen 7 260 16GB 512GB SSD RTX5060-8GB 115W Freedos 16" Wuxga 165Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Lenovo Loq 15IRX10 83JE00JQTR I7-13650HX 16GB Ddr5 1tb SSD RTX5060 8gb Tgp 100W 15.6" IPS 144Hz Freedos</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Puslu Sarı MHFD4TU/A</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 17 B13WFKG-091XTR Intel Core i7 13620H 16GB 1TB SSD RTX5060 Freedos 17.3" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
     <t>MSI CYBORG 15 B13WEKG-613XTR Intel Core I7 13620H 16GB 1TB SSD RTX5050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
   </si>
   <si>
-    <t>Lenovo LOQ Essential AMD Ryzen 7 7735HS 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar 83S00033TR</t>
-  </si>
-  <si>
-    <t>MSI CYBORG 15 A13UC-2087XTR Intel Core i5 13420H 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFG4TU/A</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5070 C7 Intel Core I7 14650HX 16GB Ram 1tb SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Yeni 2025 MatePad 11.5" PaperMatte 8GB 256GB Tablet + Klavye</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Puslu Sarı MHFD4TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Pastel Pembe  MHFH4TU/A</t>
-  </si>
-  <si>
-    <t>Ideapad Slim 3 AMD Ryzen 5-7520U 8GB 512GB SSD 15.6" FHD Dizüstü Bilgisayar 82XQ00RWTX</t>
-  </si>
-  <si>
-    <t>Pro MP275W E2 27" 120Hz 1ms FHD Flat IPS Adaptive-Sync Monitör</t>
-  </si>
-  <si>
-    <t>IdeaPad Slim3 Intel Core i5-13420H 16GB 512GB SSD 15.3" WUXGA FreeDOS  Dizüstü Bilgisayar 83K1003MTR</t>
-  </si>
-  <si>
-    <t>Dynamic Grey Masajlı Oyuncu Koltuğu</t>
-  </si>
-  <si>
-    <t>Asus Tuf Gaming A16 FA608UM-RV130 Amd Ryzen 7 260 16GB 512GB SSD RTX5060-8GB 115W Freedos 16" Wuxga 165Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>MSI CYBORG 17 B13WFKG-091XTR Intel Core i7 13620H 16GB 1TB SSD RTX5060 Freedos 17.3" FHD 144Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Excalibur E27FVC-E 27" 300HZ 1MS 400NIT Fast VA Curved HDR10 Oyuncu Monitörü</t>
-  </si>
-  <si>
-    <t>Asus Tuf Gaming F16 FX608JMR-RV078 Intel Core I7 14650HX 32GB 1 Tb SSD RTX5060-8GB 115W Freedos 16" 165Hz Wuxga Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 AMD Ryzen 7 7735HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K70098TR</t>
-  </si>
-  <si>
-    <t>Lenovo Loq 15IRX10 83JE00JQTR I7-13650HX 16GB Ddr5 1tb SSD RTX5060 8gb Tgp 100W 15.6" IPS 144Hz Freedos</t>
-  </si>
-  <si>
-    <t>Victus 15-FA2051NT Intel Core i5-14450HX 24G 1TB SSD RTX4050 6GB Freedos 15.6" FHD IPS 144Hz D2QG6EA</t>
-  </si>
-  <si>
-    <t>Rion R10 24" 165hz 1ms Fhd Va Curved Gaming Monitör (sıfır Ölü Piksel Garantili)</t>
-  </si>
-  <si>
-    <t>MSI KATANA 17 HX B14WFK-217TR Intel Core i9 14900HX 32GB 1TB SSD RTX5060 Windows 11 Home 17.3" QHD 240Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Aspire Lite Intel Celeron-N4500 8GB 256GB SSD 15.6" FHD DOS (İşletim Sistemsiz) Laptop NX.J9SEY.001</t>
-  </si>
-  <si>
-    <t>Beyaz Oyuncu Masası 160x60, Bilgisayar Masası, Gamer Masası, Gaming Masa, Metal Ayaklı</t>
-  </si>
-  <si>
-    <t>Apple Macbook Air 13.6 M2 M3 M4 M5 A2681 A3113 A3240 A3449 Kristal Kılıf Şeffaf Tam Koruma Kapak</t>
-  </si>
-  <si>
-    <t>ASUS TUF Gaming F16 FX608JMR-RV075 Intel Core i7 14650HX 16GB 1TB SSD RTX5060 Freedos 16" Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFA4TU/A</t>
-  </si>
-  <si>
-    <t>Ideapad Slim 3 Intel N100 4gb Ram 128GB Ssd 15.6'' 82XB009GTX</t>
-  </si>
-  <si>
-    <t>Excalibur G915 i7-13620H 32GB 1TB 8GB RTX5070 165Hz 16" Freedos Gaming Laptop G915.1362-DF70X-C</t>
-  </si>
-  <si>
-    <t>Excalibur G870 i7-13620H 32GB 2TB 115W RTX5060 165Hz 15.6" Freedos Gaming Laptop G870.1362-DX60X-C</t>
-  </si>
-  <si>
-    <t>Asus Zenbook S 16 UM5606WA-RK411W AMD Ryzen AI 9 HX 370 32GB 1TB SSD Windows 11 Home 16" Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
     <t>Seagate 4TB Skyhawk RV ST4000VX016 3.5" 5900Rpm 256 MB 7x24 Güvenlik Hdd (Resmi Distribitör Ürünü)</t>
   </si>
   <si>
-    <t>Lenovo IdeaPad Slim 3 Intel Core i5 13420H 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K1003MTR</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X5T-5050 C7 Intel Core I5 13500HX 16GB Ram 1tb SSD RTX5050 16" Wuxga 165Hz IPS Freedos Oyuncu Laptop</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M4 16GB 256GB SSD macOS 15" Taşınabilir Bilgisayar Gök Mavisi MC7A4TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gök Mavisi MDHH4TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFF4TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M4 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gece Yarısı MW133TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFC4TU/A</t>
-  </si>
-  <si>
-    <t>Casper Excalibur G915 Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 16" 165Hz Taşınabilir Bilgisayar G915.1362-DF60X-C</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 15" Taşınabilir Bilgisayar Gece Yarısı MDVH4TU/A</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5060 C2 Intel Core I7 14650HX 32GB Ram 1tb SSD RTX5060 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Lenovo LOQE AMD Ryzen 7 7735HS 16GB 512GB SSD RTX4050 Freedos 15.6" Taşınabilir Bilgisayar 83S0002YTR</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 Intel N100 8GB 128GB SSD Windows 11 Home 15.6" FHD Taşınabilir Bilgisayar 82XB00HMTX</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7535HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K7009ETR</t>
-  </si>
-  <si>
-    <t>Triline Nb F160+FP Gazlı Çift Kol Monitör Standı 17-30" Ekran ve 10-17" Dizüstü Bilgisayar İçin Metal</t>
-  </si>
-  <si>
-    <t>HP AI 15 Intel Core Ultra 5 225U 16GB 512GB SSD Freedos 15.6" Taşınabilir Bilgisayar D51E0EA</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5070 C2 Intel Core i7 14650HX 32GB 1TB SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Lenovo Case 15.6" Toploader T210 Taşınabilir Bilgisayar Çantası Gri GX40Q17231</t>
-  </si>
-  <si>
-    <t>Hp Prelude 15.6" Bilgisayar Çantası Gri 2Z8P4AA</t>
+    <t>CASPER</t>
+  </si>
+  <si>
+    <t>Game Garaj</t>
+  </si>
+  <si>
+    <t>Flinder</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
   </si>
   <si>
     <t>MSI</t>
   </si>
   <si>
-    <t>Lenovo</t>
+    <t>Next Gaming</t>
   </si>
   <si>
     <t>Apple</t>
   </si>
   <si>
-    <t>Game Garaj</t>
+    <t>Techmaster</t>
+  </si>
+  <si>
+    <t>LENOVO</t>
   </si>
   <si>
     <t>Huawei</t>
   </si>
   <si>
-    <t>Fashcolle</t>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>ACER</t>
   </si>
   <si>
     <t>Asus</t>
   </si>
   <si>
-    <t>CASPER</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>James Donkey</t>
-  </si>
-  <si>
-    <t>ACER</t>
-  </si>
-  <si>
-    <t>Flinder</t>
+    <t>Canon</t>
   </si>
   <si>
     <t>ASUS</t>
   </si>
   <si>
+    <t>TEKNETSTORE</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Triline</t>
+  </si>
+  <si>
+    <t>Casper</t>
+  </si>
+  <si>
     <t>Seagate</t>
   </si>
   <si>
-    <t>Casper</t>
-  </si>
-  <si>
-    <t>Triline</t>
-  </si>
-  <si>
-    <t>37939</t>
+    <t>7899</t>
+  </si>
+  <si>
+    <t>53499</t>
+  </si>
+  <si>
+    <t>2799.90</t>
+  </si>
+  <si>
+    <t>39799</t>
+  </si>
+  <si>
+    <t>92049.16</t>
+  </si>
+  <si>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>30950</t>
+  </si>
+  <si>
+    <t>37875</t>
+  </si>
+  <si>
+    <t>448.41</t>
+  </si>
+  <si>
+    <t>27199</t>
+  </si>
+  <si>
+    <t>13999</t>
+  </si>
+  <si>
+    <t>26989</t>
+  </si>
+  <si>
+    <t>28499</t>
+  </si>
+  <si>
+    <t>35999</t>
+  </si>
+  <si>
+    <t>14199</t>
+  </si>
+  <si>
+    <t>78999</t>
+  </si>
+  <si>
+    <t>66000</t>
+  </si>
+  <si>
+    <t>2006.31</t>
+  </si>
+  <si>
+    <t>39999</t>
+  </si>
+  <si>
+    <t>15006.81</t>
+  </si>
+  <si>
+    <t>43522</t>
+  </si>
+  <si>
+    <t>20949</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>69999</t>
+  </si>
+  <si>
+    <t>37999</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>13480</t>
+  </si>
+  <si>
+    <t>48223.33</t>
+  </si>
+  <si>
+    <t>63662.52</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>89000</t>
+  </si>
+  <si>
+    <t>5099</t>
+  </si>
+  <si>
+    <t>537.79</t>
+  </si>
+  <si>
+    <t>74880</t>
+  </si>
+  <si>
+    <t>569</t>
+  </si>
+  <si>
+    <t>4299</t>
+  </si>
+  <si>
+    <t>27399</t>
+  </si>
+  <si>
+    <t>78998.99</t>
+  </si>
+  <si>
+    <t>38225</t>
+  </si>
+  <si>
+    <t>16699</t>
+  </si>
+  <si>
+    <t>62261</t>
+  </si>
+  <si>
+    <t>48990</t>
+  </si>
+  <si>
+    <t>64599</t>
+  </si>
+  <si>
+    <t>70998.99</t>
+  </si>
+  <si>
+    <t>38949</t>
+  </si>
+  <si>
+    <t>54942.26</t>
+  </si>
+  <si>
+    <t>61599</t>
+  </si>
+  <si>
+    <t>42800</t>
+  </si>
+  <si>
+    <t>58299</t>
   </si>
   <si>
     <t>50420</t>
   </si>
   <si>
-    <t>39799</t>
-  </si>
-  <si>
-    <t>35999</t>
-  </si>
-  <si>
-    <t>43577.82</t>
-  </si>
-  <si>
-    <t>70998.99</t>
-  </si>
-  <si>
-    <t>13999</t>
-  </si>
-  <si>
-    <t>42800</t>
-  </si>
-  <si>
-    <t>37994</t>
-  </si>
-  <si>
-    <t>20949</t>
-  </si>
-  <si>
-    <t>5099</t>
-  </si>
-  <si>
-    <t>27249</t>
-  </si>
-  <si>
-    <t>4649</t>
-  </si>
-  <si>
-    <t>55470.17</t>
-  </si>
-  <si>
-    <t>58299</t>
-  </si>
-  <si>
-    <t>7899</t>
-  </si>
-  <si>
-    <t>75899</t>
-  </si>
-  <si>
-    <t>30950</t>
-  </si>
-  <si>
-    <t>61350.47</t>
-  </si>
-  <si>
-    <t>48223.33</t>
-  </si>
-  <si>
-    <t>3289</t>
-  </si>
-  <si>
-    <t>92049.16</t>
-  </si>
-  <si>
-    <t>14199</t>
-  </si>
-  <si>
-    <t>2799.90</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>69999</t>
-  </si>
-  <si>
-    <t>38950</t>
-  </si>
-  <si>
-    <t>13480</t>
-  </si>
-  <si>
-    <t>87949</t>
-  </si>
-  <si>
-    <t>68137.94</t>
-  </si>
-  <si>
-    <t>78999</t>
-  </si>
-  <si>
-    <t>7850</t>
-  </si>
-  <si>
-    <t>28999</t>
-  </si>
-  <si>
-    <t>53499</t>
-  </si>
-  <si>
-    <t>58999</t>
-  </si>
-  <si>
-    <t>79500</t>
-  </si>
-  <si>
-    <t>38505.48</t>
-  </si>
-  <si>
-    <t>63662.52</t>
-  </si>
-  <si>
-    <t>43932.01</t>
-  </si>
-  <si>
-    <t>64599</t>
-  </si>
-  <si>
-    <t>89999</t>
-  </si>
-  <si>
-    <t>71386.10</t>
-  </si>
-  <si>
-    <t>39999</t>
-  </si>
-  <si>
-    <t>16949</t>
-  </si>
-  <si>
-    <t>26999</t>
-  </si>
-  <si>
-    <t>4299</t>
-  </si>
-  <si>
-    <t>28499</t>
-  </si>
-  <si>
-    <t>78998.99</t>
-  </si>
-  <si>
-    <t>481.54</t>
-  </si>
-  <si>
-    <t>569</t>
+    <t>7954</t>
+  </si>
+  <si>
+    <t>4.3/5</t>
+  </si>
+  <si>
+    <t>4.8/5</t>
+  </si>
+  <si>
+    <t>4.6/5</t>
+  </si>
+  <si>
+    <t>4.9/5</t>
+  </si>
+  <si>
+    <t>5.0/5</t>
+  </si>
+  <si>
+    <t>4.2/5</t>
+  </si>
+  <si>
+    <t>4.5/5</t>
+  </si>
+  <si>
+    <t>4.4/5</t>
+  </si>
+  <si>
+    <t>3.1/5</t>
   </si>
   <si>
     <t>4.1/5</t>
   </si>
   <si>
+    <t>4.0/5</t>
+  </si>
+  <si>
+    <t>5/5</t>
+  </si>
+  <si>
     <t>4.7/5</t>
   </si>
   <si>
-    <t>4.6/5</t>
-  </si>
-  <si>
-    <t>4.9/5</t>
-  </si>
-  <si>
-    <t>4.5/5</t>
-  </si>
-  <si>
-    <t>4.8/5</t>
-  </si>
-  <si>
-    <t>4.4/5</t>
-  </si>
-  <si>
-    <t>4.2/5</t>
-  </si>
-  <si>
-    <t>4.3/5</t>
-  </si>
-  <si>
-    <t>5/5</t>
-  </si>
-  <si>
-    <t>4.0/5</t>
-  </si>
-  <si>
-    <t>3.1/5</t>
+    <t>369</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>31</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>1959</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2747</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>238</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5789</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>27</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>1959</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>99</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>2747</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>Acer</t>
   </si>
 </sst>
 </file>
@@ -603,10 +624,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -896,11 +913,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="122" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -928,16 +944,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -948,16 +964,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -968,16 +984,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -988,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1008,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1025,19 +1041,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1045,19 +1061,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1065,19 +1081,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1085,19 +1101,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1105,19 +1121,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1125,19 +1141,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1145,19 +1161,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1168,16 +1184,16 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1185,19 +1201,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1205,19 +1221,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1225,19 +1241,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F17" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1245,19 +1261,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1265,19 +1281,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1285,19 +1301,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F20" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1305,19 +1321,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1325,19 +1341,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1345,19 +1361,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1365,19 +1381,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1385,19 +1401,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F25" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1405,19 +1421,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1425,19 +1441,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1445,19 +1461,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1465,19 +1481,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
         <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1488,16 +1504,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1505,19 +1521,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F31" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1525,19 +1541,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
         <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1545,19 +1561,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1565,19 +1581,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F34" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -1585,19 +1601,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -1605,19 +1621,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F36" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1625,19 +1641,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F37" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -1645,19 +1661,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
         <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -1665,19 +1681,19 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -1685,19 +1701,19 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1705,19 +1721,19 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -1725,19 +1741,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -1745,19 +1761,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F43" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1765,19 +1781,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F44" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -1785,19 +1801,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F45" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -1805,19 +1821,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -1825,19 +1841,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E47" t="s">
         <v>131</v>
       </c>
       <c r="F47" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -1845,19 +1861,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E48" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -1865,19 +1881,19 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="E49" t="s">
         <v>129</v>
       </c>
       <c r="F49" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -1885,19 +1901,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E50" t="s">
         <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -1905,19 +1921,19 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F51" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
@@ -1925,19 +1941,19 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E52" t="s">
         <v>129</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -1945,19 +1961,19 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E53" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F53" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
@@ -1965,19 +1981,19 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E54" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F54" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -1985,19 +2001,19 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F55" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -2005,19 +2021,19 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E56" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F56" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -2025,19 +2041,19 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -2045,19 +2061,19 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E58" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F58" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -2065,19 +2081,19 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F59" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -2085,19 +2101,19 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -2105,19 +2121,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="E61" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F61" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -2125,19 +2141,19 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F62" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -2145,19 +2161,19 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E63" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -2165,19 +2181,19 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E64" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F64" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -2185,19 +2201,19 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="E65" t="s">
         <v>129</v>
       </c>
       <c r="F65" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -2205,19 +2221,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E66" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F66" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -2225,19 +2241,19 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F67" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -2245,19 +2261,19 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E68" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F68" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -2265,19 +2281,19 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E69" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -2285,16 +2301,16 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F70" t="s">
         <v>153</v>
@@ -2305,19 +2321,19 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -2325,19 +2341,19 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -2345,19 +2361,19 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F73" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -2365,19 +2381,19 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E74" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F74" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -2385,19 +2401,19 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C75" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F75" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -2408,16 +2424,16 @@
         <v>44</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D76" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F76" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -2425,19 +2441,19 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F77" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -2445,19 +2461,19 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D78" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="F78" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -2465,19 +2481,19 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C79" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F79" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -2485,19 +2501,19 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -2505,19 +2521,19 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="E81" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F81" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -2525,19 +2541,19 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D82" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F82" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -2545,19 +2561,19 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="E83" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F83" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -2565,19 +2581,19 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E84" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F84" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -2585,19 +2601,19 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F85" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -2605,19 +2621,19 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D86" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E86" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F86" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -2625,19 +2641,19 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E87" t="s">
         <v>131</v>
       </c>
       <c r="F87" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -2645,19 +2661,19 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C88" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E88" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F88" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -2665,19 +2681,19 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D89" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="E89" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F89" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -2685,19 +2701,19 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D90" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F90" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -2705,16 +2721,16 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E91" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F91" t="s">
         <v>165</v>
@@ -2725,19 +2741,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C92" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D92" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="E92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F92" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -2745,19 +2761,19 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C93" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E93" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F93" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -2765,19 +2781,19 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E94" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F94" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -2785,19 +2801,19 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="E95" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F95" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -2805,19 +2821,19 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D96" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F96" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -2825,19 +2841,19 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D97" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E97" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F97" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -2845,19 +2861,19 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D98" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E98" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F98" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -2865,19 +2881,19 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C99" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D99" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F99" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -2885,19 +2901,19 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D100" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E100" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F100" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -2905,19 +2921,19 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D101" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E101" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F101" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -2925,19 +2941,19 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C102" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D102" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E102" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F102" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -2945,19 +2961,19 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C103" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D103" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E103" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F103" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -2965,19 +2981,19 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="C104" t="s">
         <v>58</v>
       </c>
       <c r="D104" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="E104" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F104" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -2985,19 +3001,19 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C105" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D105" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E105" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F105" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -3005,19 +3021,19 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D106" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E106" t="s">
         <v>129</v>
       </c>
       <c r="F106" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -3025,19 +3041,19 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D107" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E107" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F107" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -3045,19 +3061,19 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E108" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F108" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -3065,19 +3081,19 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D109" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="E109" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F109" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -3085,19 +3101,19 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E110" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="F110" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -3105,19 +3121,19 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D111" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E111" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F111" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -3125,19 +3141,19 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D112" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E112" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F112" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -3145,19 +3161,19 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E113" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F113" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
@@ -3165,19 +3181,19 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D114" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E114" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F114" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -3188,16 +3204,16 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D115" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E115" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F115" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -3205,19 +3221,19 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D116" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E116" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F116" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -3225,19 +3241,19 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D117" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E117" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="F117" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -3245,19 +3261,19 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C118" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D118" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E118" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F118" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -3265,19 +3281,19 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D119" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E119" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F119" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
@@ -3285,19 +3301,19 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C120" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D120" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E120" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F120" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -3305,19 +3321,19 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C121" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D121" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E121" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F121" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
@@ -3325,19 +3341,19 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C122" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D122" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E122" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -3345,19 +3361,19 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D123" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E123" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F123" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -3365,19 +3381,19 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D124" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E124" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F124" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -3385,19 +3401,19 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C125" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D125" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E125" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F125" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -3405,19 +3421,19 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C126" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D126" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="E126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F126" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -3425,19 +3441,219 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D127" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="E127" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F127" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
+      </c>
+      <c r="D128" t="s">
+        <v>104</v>
+      </c>
+      <c r="E128" t="s">
+        <v>138</v>
+      </c>
+      <c r="F128" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129" t="s">
+        <v>71</v>
+      </c>
+      <c r="D129" t="s">
+        <v>95</v>
+      </c>
+      <c r="E129" t="s">
+        <v>133</v>
+      </c>
+      <c r="F129" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>52</v>
+      </c>
+      <c r="C130" t="s">
+        <v>70</v>
+      </c>
+      <c r="D130" t="s">
+        <v>123</v>
+      </c>
+      <c r="E130" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" t="s">
+        <v>70</v>
+      </c>
+      <c r="D131" t="s">
+        <v>93</v>
+      </c>
+      <c r="E131" t="s">
+        <v>132</v>
+      </c>
+      <c r="F131" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" t="s">
+        <v>64</v>
+      </c>
+      <c r="D132" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132" t="s">
+        <v>131</v>
+      </c>
+      <c r="F132" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133" t="s">
+        <v>55</v>
+      </c>
+      <c r="C133" t="s">
+        <v>62</v>
+      </c>
+      <c r="D133" t="s">
+        <v>126</v>
+      </c>
+      <c r="E133" t="s">
         <v>135</v>
+      </c>
+      <c r="F133" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>59</v>
+      </c>
+      <c r="D134" t="s">
+        <v>79</v>
+      </c>
+      <c r="E134" t="s">
+        <v>130</v>
+      </c>
+      <c r="F134" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>32</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>105</v>
+      </c>
+      <c r="E135" t="s">
+        <v>139</v>
+      </c>
+      <c r="F135" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" t="s">
+        <v>58</v>
+      </c>
+      <c r="D136" t="s">
+        <v>97</v>
+      </c>
+      <c r="E136" t="s">
+        <v>138</v>
+      </c>
+      <c r="F136" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" t="s">
+        <v>58</v>
+      </c>
+      <c r="D137" t="s">
+        <v>78</v>
+      </c>
+      <c r="E137" t="s">
+        <v>129</v>
+      </c>
+      <c r="F137" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/UcuzBilgisayar/WebScrapper/BILGISAYAR_URUNLERI.xlsx
+++ b/UcuzBilgisayar/WebScrapper/BILGISAYAR_URUNLERI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5C3A02D28638C25E/Desktop/ito-bilgisayar-urunleri/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c3a02d28638c25e/Desktop/ito-bilgisayar-urunleri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_7309C2F9368B092D02610883D52F35C378783EAB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{451D7188-90AB-4AA5-91DE-9F1A1FAAFFE0}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_7A2DE3FBBAA34F07466108FF756F19177878FDF2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F99740D-EE9B-4AE1-BA20-E532CC3CAAD5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="400">
   <si>
     <t>Ürün adı</t>
   </si>
@@ -37,541 +37,1189 @@
     <t>Yorum sayısı</t>
   </si>
   <si>
+    <t>Macbook Air M2 M3 M4 M5 13.6 A3113 A3240 A2681 ile Uyumlu Parlak Simli Şeffaf Kılıf Kapak Koruma</t>
+  </si>
+  <si>
+    <t>Pro MP275W E2 27" 120Hz 1ms FHD Flat IPS Adaptive-Sync Monitör</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFG4TU/A</t>
+  </si>
+  <si>
+    <t>Apple Macbook Neo 13 inç A3404 / A18 Pro Ekran Koruyucu Nano Esnek Kırılmaz Film Çizilmez HD Şeffaf</t>
+  </si>
+  <si>
+    <t>LOQE i5-13450HX 16GB 512GB SSD 15.6" FHD 144Hz RTX 5050 8GB GDDR7 FreeDOS 83SC000QTR</t>
+  </si>
+  <si>
+    <t>OMEN Slim Gaming 16-AN0025NT Intel Core Ultra 7-255H 24GB 1TB SSD RTX5070 240Hz DOS 16" CJ8V8EA</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M4 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gece Yarısı MW133TU/A</t>
+  </si>
+  <si>
+    <t>Ideapad Slim 3 AMD Ryzen 5-7520U 8GB 512GB SSD 15.6" FHD Dizüstü Bilgisayar 82XQ00RWTX</t>
+  </si>
+  <si>
+    <t>Galaxy Tab A11+ 6GB 128GB Gri Tablet</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7535HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K7009ETR</t>
+  </si>
+  <si>
+    <t>Nirvana Intel Celeron N4020 4GB RAM 120GB SSD Windows 11 Home 15.6" Hd Laptop C370.4020-4C00B</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gök Mavisi MDHH4TU/A</t>
+  </si>
+  <si>
+    <t>Siyah/Beyaz Oyuncu Masası 60x140 Cm, Beyaz Renk Bilgisayar Masası, Gamer Masası, Gaming Masa</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X5T-5050 C7 Intel Core I5 13500HX 16GB Ram 1tb SSD RTX5050 16" Wuxga 165Hz IPS Freedos Oyuncu Laptop</t>
+  </si>
+  <si>
+    <t>TP-Link Tapo C200 / C210 / C220 Uyumlu Kamera Duvar Askı Aparatı - Dikkat: C200C ile Uyumlu Değildir</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 AMD Ryzen 7 7735HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K70098TR</t>
+  </si>
+  <si>
+    <t>Victus 15-FA2051NT Intel Core i5-14450HX 24G 1TB SSD RTX4050 6GB Freedos 15.6" FHD IPS 144Hz D2QG6EA</t>
+  </si>
+  <si>
+    <t>Lenovo LOQE AMD Ryzen 7 7735HS 16GB 512GB SSD RTX4050 Freedos 15.6" Taşınabilir Bilgisayar 83S0002YTR</t>
+  </si>
+  <si>
+    <t>IdeaPad Slim3 Intel Core i5-13420H 16GB 512GB SSD 15.3" WUXGA FreeDOS  Dizüstü Bilgisayar 83K1003MTR</t>
+  </si>
+  <si>
+    <t>Zero 2 W</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 B13WEKG-613XTR Intel Core I7 13620H 16GB 1TB SSD RTX5050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple Macbook Air 13.6 M2 M3 M4 M5 A2681 A3113 A3240 A3449 Kristal Kılıf Şeffaf Tam Koruma Kapak</t>
+  </si>
+  <si>
     <t>Excalibur E27FVC-E 27" 300HZ 1MS 400NIT Fast VA Curved HDR10 Oyuncu Monitörü</t>
   </si>
   <si>
-    <t>Game Garaj Slayer X5T-5050 C7 Intel Core I5 13500HX 16GB Ram 1tb SSD RTX5050 16" Wuxga 165Hz IPS Freedos Oyuncu Laptop</t>
+    <t>Asus Tuf Gaming F16 FX608JMR-RV078 Intel Core I7 14650HX 32GB 1 Tb SSD RTX5060-8GB 115W Freedos 16" 165Hz Wuxga Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>JDP15 15,6″ 60Hz Full HD Taşınabilir IPS Monitör</t>
+  </si>
+  <si>
+    <t>HP AI 15 Intel Core Ultra 5 225U 16GB 512GB SSD Freedos 15.6" Taşınabilir Bilgisayar D51E0EA</t>
+  </si>
+  <si>
+    <t>Ideapad Slim 3 Intel N100 4gb Ram 128GB Ssd 15.6'' 82XB009GTX</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M4 16GB 256GB SSD macOS 15" Taşınabilir Bilgisayar Gök Mavisi MC7A4TU/A</t>
   </si>
   <si>
     <t>Beyaz Oyuncu Masası 160x60, Bilgisayar Masası, Gamer Masası, Gaming Masa, Metal Ayaklı</t>
   </si>
   <si>
+    <t>Orion Cube 3x Tuştan Değişen RGB Fanlı M-Atx Boş Bilgisayar Kasası Beyaz</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5070 C2 Intel Core i7 14650HX 32GB 1TB SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
+    <t>TUF Gaming A15 FA506NCG-HN206-Gaming AMD Ryzen 7 7445HS 16GB 512GB SSD RTX 3050 15.6" FHD IPS Fdos</t>
+  </si>
+  <si>
+    <t>LOQE AMD Ryzen 7-7735HS 16GB 512GB SSD 15.6" FHD 144Hz RTX4050 6GB FreeDOS Gaming Laptop 83S0002YTR</t>
+  </si>
+  <si>
+    <t>Yüksek Kalite Metal 360 Dönebilen Ayarlanabilir Telefon Ve Tablet Tutucu Masa Üstü Standı Siyah</t>
+  </si>
+  <si>
+    <t>Yeni 2025 MatePad 11.5" PaperMatte 8GB 256GB Tablet + Klavye</t>
+  </si>
+  <si>
+    <t>ASUS TUF Gaming F16 FX608JMR-RV075 Intel Core i7 14650HX 16GB 1TB SSD RTX5060 Freedos 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFF4TU/A</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5070 C7 Intel Core I7 14650HX 16GB Ram 1tb SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
     <t>Lenovo LOQ Essential AMD Ryzen 7 7735HS 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar 83S00033TR</t>
   </si>
   <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFA4TU/A</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 Intel Core i5 13420H 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K1003MTR</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 17 B13WFKG-091XTR Intel Core i7 13620H 16GB 1TB SSD RTX5060 Freedos 17.3" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Hp Omen 16-AM0017NT Core 7-240H 32GB 1tb SSD 8gb RTX5060 16" Freedos BQ1Z0EA Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFC4TU/A</t>
+  </si>
+  <si>
+    <t>Lenovo Loq 15IRX10 83JE00JQTR I7-13650HX 16GB Ddr5 1tb SSD RTX5060 8gb Tgp 100W 15.6" IPS 144Hz Freedos</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Yıldız Işığı MDHA4TU/A</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 B13WFKG-495XTR Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Asus Tuf Gaming A16 FA608UM-RV130 Amd Ryzen 7 260 16GB 512GB SSD RTX5060-8GB 115W Freedos 16" Wuxga 165Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Asus Vivobook 15 X1504VA-BQ5390W Intel Core 5 120U 8GB 512GB SSD Windows 11 Home 15.6" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Game Garaj Slayer X7T-5060 C2 Intel Core I7 14650HX 32GB Ram 1tb SSD RTX5060 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
+  </si>
+  <si>
+    <t>Casper Nirvana S100 Intel Core i7 13620H 16GB 1TB SSD Freedos 300Nit 16" Taşınabilir Bilgisayar S100.1362-BF00X-G-F</t>
+  </si>
+  <si>
+    <t>Asus Zenbook S 16 UM5606WA-RK411W AMD Ryzen AI 9 HX 370 32GB 1TB SSD Windows 11 Home 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 A13VE-2268XTRNN Intel Core i5 13420H 16GB 512GB SSD RTX4050 Freedos 15.6" FHD Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Pastel Pembe  MHFH4TU/A</t>
+  </si>
+  <si>
     <t>MSI KATANA 17 HX B14WFK-217TR Intel Core i9 14900HX 32GB 1TB SSD RTX5060 Windows 11 Home 17.3" QHD 240Hz Taşınabilir Bilgisayar</t>
   </si>
   <si>
-    <t>Orion Cube 3x Tuştan Değişen RGB Fanlı M-Atx Boş Bilgisayar Kasası Beyaz</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 AMD Ryzen 7 7735HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K70098TR</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Pastel Pembe  MHFH4TU/A</t>
-  </si>
-  <si>
-    <t>Macbook Air M2 M3 M4 M5 13.6 A3113 A3240 A2681 ile Uyumlu Parlak Simli Şeffaf Kılıf Kapak Koruma</t>
-  </si>
-  <si>
-    <t>IdeaPad Slim3 Intel Core i5-13420H 16GB 512GB SSD 15.3" WUXGA FreeDOS  Dizüstü Bilgisayar 83K1003MTR</t>
-  </si>
-  <si>
-    <t>Yeni 2025 MatePad 11.5" PaperMatte 8GB 256GB Tablet + Klavye</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7535HS 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K7009ETR</t>
-  </si>
-  <si>
-    <t>HP AI 15 Intel Core Ultra 5 225U 16GB 512GB SSD Freedos 15.6" Taşınabilir Bilgisayar D51E0EA</t>
+    <t>Monster Abra A5 V22.1.14 Intel Core i7 13620H 24 GB RAM 1 TB SSD 8 GB RTX 5050 FreeDOS 15,6" FHD 144 Hz Oyun Bilgisayarı</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 15" Taşınabilir Bilgisayar Gece Yarısı MDVH4TU/A</t>
+  </si>
+  <si>
+    <t>Casper Excalibur G870 Intel Core i7 13620H 24GB 1TB SSD RTX5060 Freedos 15.6" 165Hz Taşınabilir Bilgisayar G870.1362-CF60X-C</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 Intel N100 8GB 128GB SSD Windows 11 Home 15.6" FHD Taşınabilir Bilgisayar 82XB00HMTX</t>
+  </si>
+  <si>
+    <t>Gigabyte Gaming A16-CVH Intel Core i7 13620H 16GB 1TB SSD RTX5060 Freedos 165Hz 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Casper Excalibur G915 Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 16" 165Hz Taşınabilir Bilgisayar G915.1362-DF60X-C</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Pastel Pembe MHFJ4TU/A</t>
+  </si>
+  <si>
+    <t>MSI KATANA 15 HX B14WFK-450XTR Intel Core i9 14900HX 32GB 1TB SSD RTX5060 Freedos Taşınabilir Bilgisayar 15.6" QHD 165Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Triline Nb F160+FP Gazlı Çift Kol Monitör Standı 17-30" Ekran ve 10-17" Dizüstü Bilgisayar İçin Metal</t>
+  </si>
+  <si>
+    <t>ASUS ROG Strix G16 G614PH-RV036 AMD Ryzen 9 8940HX 16GB 1TB SSD RTX5050 Freedos 16" WUXGA 165Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Asus TUF Gaming FX607VU-RL017 Intel Core 5 210H 16GB 512GB SSD RTX4050 Freedos 16" Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Puslu Sarı MHFD4TU/A</t>
+  </si>
+  <si>
+    <t>Asus Zenbook Duo UX8406CA-PZ208W Intel Core Ultra 9 285H 32GB 2TB SSD Windows 11 Home 14" OLED Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Lenovo Case 15.6" Toploader T210 Taşınabilir Bilgisayar Çantası Siyah GX40Q17229</t>
+  </si>
+  <si>
+    <t>Huawei Matebook D16 2024 Intel Core i5 12450H 8GB 512GB SSD Freedos 16" IPS Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Hp Prelude 15.6" Bilgisayar Çantası Gri 2Z8P4AA</t>
+  </si>
+  <si>
+    <t>Lenovo Legion Pro 5 16ADR10 AMD Ryzen 9 8940HX 32GB 1TB SSD RTX 5070 8GB 16" WQXGA (2560X1600) IPS Panel 240Hz 115W Freedos Taşınabilir Dizüstü Bilgisayar 83LT0046TR</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 Intel Celeron N100 4GB 128GB SSD Windows 11 Home 15.6" Taşınabilir Bilgisayar 82XB009GTX</t>
+  </si>
+  <si>
+    <t>MSI THIN A15 B7VE-076XTR AMD Ryzen 5 7535HS 16GB 512GB SSD RTX4050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Lenovo Loqe I5-13450HX 16GB 512GB SSD 15.6" Fhd 144Hz Rtx 5050 8gb Gddr7 Freedos 83SC000QTR</t>
+  </si>
+  <si>
+    <t>Lenovo Loq 15IRX10 Gtı1 Intel Core I5 13450HX 24GB 1tb SSD RTX5050 Freedos 15.6" Fhd 83JE00EBTR</t>
+  </si>
+  <si>
+    <t>Lenovo Loq 15IRX10 83JE00JQTR-02 I7-13650HX 32GB Ddr5 1tb SSD RTX5060 8gb Tgp 100W 15.6" IPS 144Hz Freedos</t>
   </si>
   <si>
     <t>MSI CYBORG 15 A13UC-2087XTR Intel Core i5 13420H 16GB 512GB SSD RTX3050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
   </si>
   <si>
-    <t>Aspire Lite Intel Celeron-N4500 8GB 256GB SSD 15.6" FHD DOS (İşletim Sistemsiz) Laptop NX.J9SEY.001</t>
-  </si>
-  <si>
-    <t>Asus Zenbook S 16 UM5606WA-RK411W AMD Ryzen AI 9 HX 370 32GB 1TB SSD Windows 11 Home 16" Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M4 16GB 256GB SSD macOS 15" Taşınabilir Bilgisayar Gök Mavisi MC7A4TU/A</t>
-  </si>
-  <si>
-    <t>Pg-46-cl-56 | E414-404-484-474 Renkli Orjinal Kartuş Seti</t>
-  </si>
-  <si>
-    <t>Lenovo LOQE AMD Ryzen 7 7735HS 16GB 512GB SSD RTX4050 Freedos 15.6" Taşınabilir Bilgisayar 83S0002YTR</t>
-  </si>
-  <si>
-    <t>Nirvana Intel Celeron N4020 4GB RAM 120GB SSD Windows 11 Home 15.6" Hd Laptop C370.4020-4C00B</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFG4TU/A</t>
-  </si>
-  <si>
-    <t>Ideapad Slim 3 AMD Ryzen 5-7520U 8GB 512GB SSD 15.6" FHD Dizüstü Bilgisayar 82XQ00RWTX</t>
-  </si>
-  <si>
-    <t>Siyah/Beyaz Oyuncu Masası 60x140 Cm, Beyaz Renk Bilgisayar Masası, Gamer Masası, Gaming Masa</t>
-  </si>
-  <si>
-    <t>ASUS TUF Gaming F16 FX608JMR-RV075 Intel Core i7 14650HX 16GB 1TB SSD RTX5060 Freedos 16" Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>LOQE AMD Ryzen 7-7735HS 16GB 512GB SSD 15.6" FHD 144Hz RTX4050 6GB FreeDOS Gaming Laptop 83S0002YTR</t>
-  </si>
-  <si>
-    <t>Apple Macbook Air 13.6 M2 M3 M4 M5 A2681 A3113 A3240 A3449 Kristal Kılıf Şeffaf Tam Koruma Kapak</t>
-  </si>
-  <si>
-    <t>Ideapad Slim 3 Intel N100 4gb Ram 128GB Ssd 15.6'' 82XB009GTX</t>
-  </si>
-  <si>
-    <t>Victus 15-FA2051NT Intel Core i5-14450HX 24G 1TB SSD RTX4050 6GB Freedos 15.6" FHD IPS 144Hz D2QG6EA</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M4 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gece Yarısı MW133TU/A</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gök Mavisi MDHH4TU/A</t>
-  </si>
-  <si>
-    <t>13" MacBook Neo Pastel Pembe 256GB</t>
-  </si>
-  <si>
-    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 15" Taşınabilir Bilgisayar Gece Yarısı MDVH4TU/A</t>
-  </si>
-  <si>
-    <t>Pro MP275W E2 27" 120Hz 1ms FHD Flat IPS Adaptive-Sync Monitör</t>
-  </si>
-  <si>
-    <t>Lenovo Case 15.6" Toploader T210 Taşınabilir Bilgisayar Çantası Siyah GX40Q17229</t>
-  </si>
-  <si>
-    <t>Asus Tuf Gaming F16 FX608JMR-RV078 Intel Core I7 14650HX 32GB 1 Tb SSD RTX5060-8GB 115W Freedos 16" 165Hz Wuxga Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Hp Prelude 15.6" Bilgisayar Çantası Gri 2Z8P4AA</t>
-  </si>
-  <si>
-    <t>Triline Nb F160+FP Gazlı Çift Kol Monitör Standı 17-30" Ekran ve 10-17" Dizüstü Bilgisayar İçin Metal</t>
-  </si>
-  <si>
-    <t>Lenovo IdeaPad Slim 3 Intel Core i5 13420H 16GB 512GB SSD Freedos 15.3" Taşınabilir Bilgisayar 83K1003MTR</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5070 C2 Intel Core i7 14650HX 32GB 1TB SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Indigo MHFF4TU/A</t>
-  </si>
-  <si>
-    <t>Lenovo Ideapad Slim 3 Intel N100 8GB 128GB SSD Windows 11 Home 15.6" FHD Taşınabilir Bilgisayar 82XB00HMTX</t>
-  </si>
-  <si>
-    <t>MSI CYBORG 15 B13WFKG-495XTR Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFC4TU/A</t>
-  </si>
-  <si>
-    <t>Casper Excalibur G915 Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 16" 165Hz Taşınabilir Bilgisayar G915.1362-DF60X-C</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5060 C2 Intel Core I7 14650HX 32GB Ram 1tb SSD RTX5060 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MHFA4TU/A</t>
-  </si>
-  <si>
-    <t>Game Garaj Slayer X7T-5070 C7 Intel Core I7 14650HX 16GB Ram 1tb SSD RTX5070 16" Qhd+ 180Hz IPS Freedos Gaming Laptop</t>
-  </si>
-  <si>
-    <t>Asus Tuf Gaming A16 FA608UM-RV130 Amd Ryzen 7 260 16GB 512GB SSD RTX5060-8GB 115W Freedos 16" Wuxga 165Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>Lenovo Loq 15IRX10 83JE00JQTR I7-13650HX 16GB Ddr5 1tb SSD RTX5060 8gb Tgp 100W 15.6" IPS 144Hz Freedos</t>
-  </si>
-  <si>
-    <t>Apple MacBook Neo A18 Pro 8GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Puslu Sarı MHFD4TU/A</t>
-  </si>
-  <si>
-    <t>MSI CYBORG 17 B13WFKG-091XTR Intel Core i7 13620H 16GB 1TB SSD RTX5060 Freedos 17.3" FHD 144Hz Taşınabilir Bilgisayar</t>
-  </si>
-  <si>
-    <t>MSI CYBORG 15 B13WEKG-613XTR Intel Core I7 13620H 16GB 1TB SSD RTX5050 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+    <t>Hp Elitebook 840 G5 Intel I5-8350U 16 Ram 500 SSD 14" Notebook - Outlet</t>
+  </si>
+  <si>
+    <t>Lenovo LOQ Intel Core i7 13700HX 16GB 512GB SSD RTX5050 Freedos 15.6" Taşınabilir Bilgisayar 83JE00WGTR</t>
+  </si>
+  <si>
+    <t>Casper Nirvana S100 Intel Core i5 13420H 16GB 500GB SSD Windows 11 Home 300Nit 16" Taşınabilir Bilgisayar S100.1342-BV00A-G-F</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 83EM00C7TR i5 13420H 8GB 512GB SSD 15.6" WUXGA (1920x1200) FreeDOS Notebook</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo A18 Pro 8GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Puslu Sarı MHFE4TU/A</t>
+  </si>
+  <si>
+    <t>HP Victus Gaming 15-FB3040NT AMD Ryzen 7 7445HS 16GB 512GB SSD RTX3050 Freedos 15.6" Taşınabilir Bilgisayar BX9V1EA</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M5 16GB 512GB SSD macOS 13" Taşınabilir Bilgisayar Gece Yarısı MDHE4TU/A</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 15IRH10 83K10061TR I7-13620H 16gb Ddr5 1tb SSD Wuxga 15.3" IPS 60Hz Freedos Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 15IRH8 I5-13420H 16 GB 512 GB SSD 15.6" FHD Freedos 83EM00KYTR</t>
+  </si>
+  <si>
+    <t>Apple MacBook Pro M5 16GB 512GB SSD macOS 14" Taşınabilir Bilgisayar Gümüş MDE44TU/A</t>
+  </si>
+  <si>
+    <t>Asus Rog Strıx G16 G615JMR-S5048 Intel I7-14650HX 16GB 512GB 8GB RTX5060 16" 2.5k 240HZ Freedos Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>24” Odyssey G3 LS24DG302EUXUF 1ms 180hz VA HDMI,DisplayPort Pivot Gaming Monitör</t>
+  </si>
+  <si>
+    <t>Medion Signium 14 S1 MD600032 Intel Core 5 120U 16GB 512GB SSD Freedos 14" 120Hz OLED Dizüstü Bilgisayar</t>
+  </si>
+  <si>
+    <t>Gamenote GK60 PRO RGB Profesyonel Oyuncu ve Yayıncı Mikrofonu - RGB Standlı USB Mikrofon</t>
+  </si>
+  <si>
+    <t>Acer Nitro V 16 ANV16-71-751Z Intel Core i7 14650HX 16GB 512GB SSD RTX4060 Windows 11 Home 16" Taşınabilir Bilgisayar NH.QTMEY.001</t>
+  </si>
+  <si>
+    <t>MAG 244F 23.8″ 1920x1080 (FHD) RAPID IPS FLAT 200Hz 0.5Ms FreeSync Premium Gaming Monitör</t>
+  </si>
+  <si>
+    <t>Lenovo LOQ 15ARP10E AMD Ryzen 7 7735HS 16GB 1TB SSD RTX 3050 6GB 15.6" FHD (1920X1080) IPS 144Hz Freedos Taşınabilir Bilgisayar 83S00032TR</t>
+  </si>
+  <si>
+    <t>ASUS ROG STRIX G16 G614PM-S5062 AMD Ryzen 9 8940HX 16GB 1TB RTX5060 Freedos 16" WQXGA 240HZ Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Lenovo Legion 5 Intel Core Ultra 7 255HX 32GB 1TB SSD RTX5070 Windows 11 Home 15.1" OLED 165Hz Taşınabilir Bilgisayar 83F00087TR</t>
+  </si>
+  <si>
+    <t>Cyborg 15 B13WEKG-613XTR i7-13620H 16GB 1TB SSD 8GB RTX5050 15.6 FHD 144Hz FreeDOS</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 15 B13WFKG-679XTR Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 15.6" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Robust Premium 7x RGB Fanlı USB 3.0 TYPE-C Gaming Bilgisayar Kasası Siyah</t>
+  </si>
+  <si>
+    <t>32GB Metal USB Flash Bellek U106</t>
+  </si>
+  <si>
+    <t>Huawei MateBook D 16 2024 16" i5-12450H UMA 16GB SSD 512GB Space Gray FreeDOS Notebook</t>
   </si>
   <si>
     <t>Seagate 4TB Skyhawk RV ST4000VX016 3.5" 5900Rpm 256 MB 7x24 Güvenlik Hdd (Resmi Distribitör Ürünü)</t>
   </si>
   <si>
-    <t>CASPER</t>
+    <t>Wifi Pro Sinyal Yaklaştırıcı Güçlendirici N300 (Xiaomi Türkiye Garantili)</t>
+  </si>
+  <si>
+    <t>Asus Vivobook 15 X1504VA-BQ5382W Intel Core 5 120U 8gb 512GB SSD Windows 11 Home 15.6" Fhd</t>
+  </si>
+  <si>
+    <t>Apple MacBook Neo 13 inç A3404 A18 Pro Şeffaf Klavye Koruyucu Ultra İnce Sıvı Toz Kalkanı (Q Klavye)</t>
+  </si>
+  <si>
+    <t>MSI CYBORG 17 B13WFKG-210XTR Intel Core i7 13620H 32GB 1TB SSD RTX5060 Freedos 17.3" FHD 144Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Apple MacBook Air M4 16GB 256GB SSD macOS 13" Taşınabilir Bilgisayar Gümüş MW0W3TU/A</t>
+  </si>
+  <si>
+    <t>Pad X8B 4GB 128GB Wi-Fi 11 inç IPS Gri Tablet</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Slim 3 16IRH10 Intel Core I5-13420H 16GB 512GB SSD 16" WUXGA (1920X1200) IPS Panel Freedos Taşınabilir Dizüstü Bilgisayar 83K20073TR</t>
+  </si>
+  <si>
+    <t>Alüminyum Ayarlı Laptop Macbook Uyumlu Notebook Yükseltici Tutucu Stand</t>
+  </si>
+  <si>
+    <t>Ravel R45 24'' 240Hz 0.5Ms Fast IPS FHD Pivot Gaming Monitör</t>
+  </si>
+  <si>
+    <t>MSI KATANA 17 HX B14WGK-046XTR Intel Core i7 14650HX 32GB 1TB SSD RTX5070 Freedos 17.3" QHD 240Hz Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>New Matepad 11.5 inç 8/256GB + Klavye Tablet Mor</t>
+  </si>
+  <si>
+    <t>GM-X1 Tuştan Değişmeli 3X RGB Fanlı Gaming Mini Akvaryum m-ATX Siyah Kasa</t>
+  </si>
+  <si>
+    <t>Hp Omen 16-AP0032NT Amd Ryzen 9 - 8940HX 32GB 1tb SSD 8gb RTX5070 16"240Hz Freedos Laptop CA8E9EA</t>
+  </si>
+  <si>
+    <t>Pad X9a 8gb 256gb Wi-fi 11.5 Inç Ips Uzay Gri Tablet</t>
+  </si>
+  <si>
+    <t>Batman Gamer Kulaklık Standı Xbox &amp;amp; Playtation Uyumlu Gamepad / Kol Tutucu Dekoratif 22 Cm Siyah</t>
+  </si>
+  <si>
+    <t>Lenovo LOQ 15IAX9E 83LK002VTR i7-12650HX 16 GB 512 GB RTX4050 15.6" FreeDOS Gaming Notebook</t>
+  </si>
+  <si>
+    <t>Huawei Matebook D16 2024 Intel Core i5 12450H 16GB 512GB SSD Windows 11 Home 16" IPS Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>4 Eksenli 360 Derece Teleskopik Tüm Tablet Ve Telefonla Uyumlu Ayaklı Stand Tablet Tutucu</t>
+  </si>
+  <si>
+    <t>Dell Vostro 3530 I7-1355U 32 GB 1 Tb SSD Windows 11 Pro Iris Xe Graphics 15.6" Full Hd Taşınabilir bilgisayar N1601PVNB3530U Cb6</t>
+  </si>
+  <si>
+    <t>Bluetooth Hoparlör Mikrofonlu Rgb Işıklı Taşınabilir Parti Speaker GTS-2129 Siyah</t>
+  </si>
+  <si>
+    <t>Asus TUF Gaming A16 FA607NUG-RL125-Gaming AMD Ryzen 7 7445HS 16GB 512GB SSD RTX 4050 6GB 16" FHD+ (1920 x 1200) WUXGA 144Hz IPS Panel Taşınabilir Bilgisayar</t>
+  </si>
+  <si>
+    <t>Gamenote H2040D RGB Aydınlatmalı Mikrofonlu Gaming Oyuncu Kulaklığı - 3.5mm Jack + USB - Beyaz</t>
+  </si>
+  <si>
+    <t>Apple MacBook Pro M5 16GB 1TB SSD macOS 14" Taşınabilir Bilgisayar Gümüş MDE54TU/A</t>
+  </si>
+  <si>
+    <t>Lenovo Legion 5 15IRX10 Intel Core i7-13650HX 32GB 1TB SSD RTX 5060 8GB 15.3" WUXGA (1920X1200) IPS 165Hz 115W Freedos Taşınabilir Bilgisayar 83LY00PYTR</t>
+  </si>
+  <si>
+    <t>Monster Abra A7 V15.5 Intel Core i5 13500H 16 GB RAM 500 SSD GB 4 GB RTX 3050 FreeDOS 17,3" 144 Hz Oyun Bilgisayarı</t>
+  </si>
+  <si>
+    <t>Yazıcı Termal Kablosuz Bağlantılı Ap Kontrol Taşınabilir Mini Yazıcı C9 Pembe</t>
+  </si>
+  <si>
+    <t>Kadın Gözlük 2’li Set – Mavi Işık Korumalı Siyah ve Leopar Çerçeveli Bilgisayar Gözlüğü</t>
+  </si>
+  <si>
+    <t>Techmaster</t>
+  </si>
+  <si>
+    <t>MSI</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Fibaks</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>Flinder</t>
   </si>
   <si>
     <t>Game Garaj</t>
   </si>
   <si>
-    <t>Flinder</t>
-  </si>
-  <si>
-    <t>Lenovo</t>
-  </si>
-  <si>
-    <t>MSI</t>
+    <t>Prtp-Prototip Elektronik &amp;amp; Hobi</t>
+  </si>
+  <si>
+    <t>Raspberry Pi</t>
+  </si>
+  <si>
+    <t>TEKNETSTORE</t>
+  </si>
+  <si>
+    <t>Asus</t>
+  </si>
+  <si>
+    <t>James Donkey</t>
   </si>
   <si>
     <t>Next Gaming</t>
   </si>
   <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Techmaster</t>
-  </si>
-  <si>
-    <t>LENOVO</t>
+    <t>ASUS</t>
   </si>
   <si>
     <t>Huawei</t>
   </si>
   <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>ACER</t>
-  </si>
-  <si>
-    <t>Asus</t>
-  </si>
-  <si>
-    <t>Canon</t>
-  </si>
-  <si>
-    <t>ASUS</t>
-  </si>
-  <si>
-    <t>TEKNETSTORE</t>
-  </si>
-  <si>
     <t>Hp</t>
   </si>
   <si>
+    <t>Asus Vivobook</t>
+  </si>
+  <si>
+    <t>Casper</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>Gigabyte</t>
+  </si>
+  <si>
     <t>Triline</t>
   </si>
   <si>
-    <t>Casper</t>
+    <t>HP Victus</t>
+  </si>
+  <si>
+    <t>Medion</t>
+  </si>
+  <si>
+    <t>Havit</t>
+  </si>
+  <si>
+    <t>Acer</t>
+  </si>
+  <si>
+    <t>GAMELİNE</t>
+  </si>
+  <si>
+    <t>Dahua</t>
   </si>
   <si>
     <t>Seagate</t>
   </si>
   <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>Honor</t>
+  </si>
+  <si>
+    <t>KTR TECH</t>
+  </si>
+  <si>
+    <t>GM Game Master</t>
+  </si>
+  <si>
+    <t>Miralux</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>Torima</t>
+  </si>
+  <si>
+    <t>GlimmerGroove</t>
+  </si>
+  <si>
+    <t>448.41</t>
+  </si>
+  <si>
+    <t>5099</t>
+  </si>
+  <si>
+    <t>43649</t>
+  </si>
+  <si>
+    <t>172.01</t>
+  </si>
+  <si>
+    <t>40019</t>
+  </si>
+  <si>
+    <t>74469</t>
+  </si>
+  <si>
+    <t>63999</t>
+  </si>
+  <si>
+    <t>20949</t>
+  </si>
+  <si>
+    <t>8669</t>
+  </si>
+  <si>
+    <t>24699.05</t>
+  </si>
+  <si>
+    <t>15006.81</t>
+  </si>
+  <si>
+    <t>76499</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>53499</t>
+  </si>
+  <si>
+    <t>189.99</t>
+  </si>
+  <si>
+    <t>30950</t>
+  </si>
+  <si>
+    <t>48219</t>
+  </si>
+  <si>
+    <t>41807</t>
+  </si>
+  <si>
+    <t>27198</t>
+  </si>
+  <si>
+    <t>2890</t>
+  </si>
+  <si>
+    <t>50420</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
     <t>7899</t>
   </si>
   <si>
-    <t>53499</t>
+    <t>74880</t>
+  </si>
+  <si>
+    <t>2999</t>
+  </si>
+  <si>
+    <t>28499</t>
+  </si>
+  <si>
+    <t>14199</t>
+  </si>
+  <si>
+    <t>65799.06</t>
   </si>
   <si>
     <t>2799.90</t>
   </si>
   <si>
-    <t>39799</t>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>78998.99</t>
+  </si>
+  <si>
+    <t>33990</t>
+  </si>
+  <si>
+    <t>37999</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>15399</t>
+  </si>
+  <si>
+    <t>69999</t>
+  </si>
+  <si>
+    <t>37979</t>
+  </si>
+  <si>
+    <t>70998.99</t>
+  </si>
+  <si>
+    <t>35999.10</t>
+  </si>
+  <si>
+    <t>38949</t>
+  </si>
+  <si>
+    <t>27434</t>
+  </si>
+  <si>
+    <t>58299</t>
+  </si>
+  <si>
+    <t>65273.84</t>
+  </si>
+  <si>
+    <t>48990</t>
+  </si>
+  <si>
+    <t>65115.22</t>
+  </si>
+  <si>
+    <t>73742.06</t>
+  </si>
+  <si>
+    <t>62261</t>
+  </si>
+  <si>
+    <t>54942.26</t>
+  </si>
+  <si>
+    <t>23420</t>
+  </si>
+  <si>
+    <t>34999</t>
+  </si>
+  <si>
+    <t>78999</t>
+  </si>
+  <si>
+    <t>38894.95</t>
+  </si>
+  <si>
+    <t>37875</t>
   </si>
   <si>
     <t>92049.16</t>
   </si>
   <si>
-    <t>1695</t>
-  </si>
-  <si>
-    <t>30950</t>
-  </si>
-  <si>
-    <t>37875</t>
-  </si>
-  <si>
-    <t>448.41</t>
-  </si>
-  <si>
-    <t>27199</t>
-  </si>
-  <si>
-    <t>13999</t>
-  </si>
-  <si>
-    <t>26989</t>
-  </si>
-  <si>
-    <t>28499</t>
+    <t>66249</t>
+  </si>
+  <si>
+    <t>89000</t>
+  </si>
+  <si>
+    <t>57990</t>
+  </si>
+  <si>
+    <t>16699</t>
+  </si>
+  <si>
+    <t>52300.21</t>
+  </si>
+  <si>
+    <t>64599</t>
+  </si>
+  <si>
+    <t>49999</t>
+  </si>
+  <si>
+    <t>86346</t>
+  </si>
+  <si>
+    <t>4299</t>
+  </si>
+  <si>
+    <t>68999</t>
+  </si>
+  <si>
+    <t>42499</t>
+  </si>
+  <si>
+    <t>42800</t>
+  </si>
+  <si>
+    <t>110999</t>
+  </si>
+  <si>
+    <t>437.79</t>
+  </si>
+  <si>
+    <t>23999</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>101701.11</t>
+  </si>
+  <si>
+    <t>38888</t>
+  </si>
+  <si>
+    <t>42254.24</t>
+  </si>
+  <si>
+    <t>51999</t>
+  </si>
+  <si>
+    <t>59873.22</t>
+  </si>
+  <si>
+    <t>72999</t>
+  </si>
+  <si>
+    <t>36939</t>
+  </si>
+  <si>
+    <t>17775</t>
+  </si>
+  <si>
+    <t>29999</t>
+  </si>
+  <si>
+    <t>26122.52</t>
+  </si>
+  <si>
+    <t>52000</t>
   </si>
   <si>
     <t>35999</t>
   </si>
   <si>
-    <t>14199</t>
-  </si>
-  <si>
-    <t>78999</t>
-  </si>
-  <si>
-    <t>66000</t>
-  </si>
-  <si>
-    <t>2006.31</t>
-  </si>
-  <si>
-    <t>39999</t>
-  </si>
-  <si>
-    <t>15006.81</t>
-  </si>
-  <si>
-    <t>43522</t>
-  </si>
-  <si>
-    <t>20949</t>
-  </si>
-  <si>
-    <t>2028</t>
-  </si>
-  <si>
-    <t>69999</t>
-  </si>
-  <si>
-    <t>37999</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>13480</t>
-  </si>
-  <si>
-    <t>48223.33</t>
-  </si>
-  <si>
-    <t>63662.52</t>
-  </si>
-  <si>
     <t>80000</t>
   </si>
   <si>
-    <t>89000</t>
-  </si>
-  <si>
-    <t>5099</t>
-  </si>
-  <si>
-    <t>537.79</t>
-  </si>
-  <si>
-    <t>74880</t>
-  </si>
-  <si>
-    <t>569</t>
-  </si>
-  <si>
-    <t>4299</t>
-  </si>
-  <si>
-    <t>27399</t>
-  </si>
-  <si>
-    <t>78998.99</t>
-  </si>
-  <si>
-    <t>38225</t>
-  </si>
-  <si>
-    <t>16699</t>
-  </si>
-  <si>
-    <t>62261</t>
-  </si>
-  <si>
-    <t>48990</t>
-  </si>
-  <si>
-    <t>64599</t>
-  </si>
-  <si>
-    <t>70998.99</t>
-  </si>
-  <si>
-    <t>38949</t>
-  </si>
-  <si>
-    <t>54942.26</t>
-  </si>
-  <si>
-    <t>61599</t>
-  </si>
-  <si>
-    <t>42800</t>
-  </si>
-  <si>
-    <t>58299</t>
-  </si>
-  <si>
-    <t>50420</t>
+    <t>27999</t>
+  </si>
+  <si>
+    <t>96300</t>
+  </si>
+  <si>
+    <t>38499</t>
+  </si>
+  <si>
+    <t>23420.14</t>
+  </si>
+  <si>
+    <t>74999</t>
+  </si>
+  <si>
+    <t>4526.21</t>
+  </si>
+  <si>
+    <t>29157.21</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>50310.27</t>
+  </si>
+  <si>
+    <t>4959</t>
+  </si>
+  <si>
+    <t>37552.41</t>
+  </si>
+  <si>
+    <t>82999</t>
+  </si>
+  <si>
+    <t>98999.10</t>
+  </si>
+  <si>
+    <t>47799</t>
+  </si>
+  <si>
+    <t>63398</t>
+  </si>
+  <si>
+    <t>2770</t>
+  </si>
+  <si>
+    <t>271.77</t>
+  </si>
+  <si>
+    <t>28999</t>
   </si>
   <si>
     <t>7954</t>
   </si>
   <si>
+    <t>719</t>
+  </si>
+  <si>
+    <t>22999</t>
+  </si>
+  <si>
+    <t>171.88</t>
+  </si>
+  <si>
+    <t>63674.31</t>
+  </si>
+  <si>
+    <t>57800.83</t>
+  </si>
+  <si>
+    <t>6749</t>
+  </si>
+  <si>
+    <t>29472.63</t>
+  </si>
+  <si>
+    <t>168.31</t>
+  </si>
+  <si>
+    <t>4799</t>
+  </si>
+  <si>
+    <t>100421.78</t>
+  </si>
+  <si>
+    <t>15999</t>
+  </si>
+  <si>
+    <t>1425.67</t>
+  </si>
+  <si>
+    <t>85448.25</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>162.67</t>
+  </si>
+  <si>
+    <t>41999</t>
+  </si>
+  <si>
+    <t>31900</t>
+  </si>
+  <si>
+    <t>345.74</t>
+  </si>
+  <si>
+    <t>44287.99</t>
+  </si>
+  <si>
+    <t>423.59</t>
+  </si>
+  <si>
+    <t>42999</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>116000</t>
+  </si>
+  <si>
+    <t>45298</t>
+  </si>
+  <si>
+    <t>749</t>
+  </si>
+  <si>
+    <t>194.02</t>
+  </si>
+  <si>
+    <t>5.0/5</t>
+  </si>
+  <si>
+    <t>4.9/5</t>
+  </si>
+  <si>
+    <t>4.5/5</t>
+  </si>
+  <si>
+    <t>3.6/5</t>
+  </si>
+  <si>
+    <t>4.1/5</t>
+  </si>
+  <si>
+    <t>4.0/5</t>
+  </si>
+  <si>
+    <t>4.8/5</t>
+  </si>
+  <si>
+    <t>4.4/5</t>
+  </si>
+  <si>
+    <t>4.6/5</t>
+  </si>
+  <si>
+    <t>4.2/5</t>
+  </si>
+  <si>
+    <t>4.7/5</t>
+  </si>
+  <si>
     <t>4.3/5</t>
   </si>
   <si>
-    <t>4.8/5</t>
-  </si>
-  <si>
-    <t>4.6/5</t>
-  </si>
-  <si>
-    <t>4.9/5</t>
-  </si>
-  <si>
-    <t>5.0/5</t>
-  </si>
-  <si>
-    <t>4.2/5</t>
-  </si>
-  <si>
-    <t>4.5/5</t>
-  </si>
-  <si>
-    <t>4.4/5</t>
-  </si>
-  <si>
-    <t>3.1/5</t>
-  </si>
-  <si>
-    <t>4.1/5</t>
-  </si>
-  <si>
-    <t>4.0/5</t>
-  </si>
-  <si>
     <t>5/5</t>
   </si>
   <si>
-    <t>4.7/5</t>
+    <t>3.9/5</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1959</t>
   </si>
   <si>
     <t>369</t>
   </si>
   <si>
-    <t>51</t>
+    <t>46</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>92</t>
   </si>
   <si>
     <t>143</t>
   </si>
   <si>
-    <t>11</t>
+    <t>23</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>4564</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>59</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>106</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>2747</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1959</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2747</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>58</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>212</t>
   </si>
   <si>
     <t>99</t>
+  </si>
+  <si>
+    <t>8323</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>2724</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>1409</t>
   </si>
 </sst>
 </file>
@@ -913,10 +1561,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="122" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="151.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -944,2716 +1597,2656 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>301</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>302</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>305</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>306</v>
       </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>307</v>
       </c>
       <c r="F8" t="s">
-        <v>148</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>308</v>
       </c>
       <c r="F9" t="s">
-        <v>149</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>309</v>
       </c>
       <c r="F10" t="s">
-        <v>150</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>305</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="F15" t="s">
-        <v>149</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>301</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>310</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="F21" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>303</v>
       </c>
       <c r="F23" t="s">
-        <v>159</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="F24" t="s">
-        <v>160</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="F25" t="s">
-        <v>161</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>312</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>308</v>
       </c>
       <c r="F27" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>199</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>305</v>
       </c>
       <c r="F28" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="E31" t="s">
-        <v>131</v>
+        <v>307</v>
       </c>
       <c r="F31" t="s">
-        <v>162</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="F32" t="s">
-        <v>147</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F33" t="s">
-        <v>165</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>134</v>
+        <v>305</v>
       </c>
       <c r="F34" t="s">
-        <v>151</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>308</v>
       </c>
       <c r="F35" t="s">
-        <v>166</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>303</v>
       </c>
       <c r="F36" t="s">
-        <v>167</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="F37" t="s">
-        <v>152</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="E38" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="F38" t="s">
-        <v>168</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>307</v>
       </c>
       <c r="F39" t="s">
-        <v>159</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s">
-        <v>137</v>
+        <v>303</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="E43" t="s">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="F43" t="s">
-        <v>171</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="E44" t="s">
-        <v>132</v>
+        <v>313</v>
       </c>
       <c r="F44" t="s">
-        <v>172</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="E45" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="F45" t="s">
-        <v>150</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>307</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="E47" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="F47" t="s">
-        <v>162</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="D48" t="s">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>307</v>
       </c>
       <c r="F48" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="E49" t="s">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="F49" t="s">
-        <v>142</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>221</v>
       </c>
       <c r="E50" t="s">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="F50" t="s">
-        <v>163</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="E51" t="s">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="F51" t="s">
-        <v>161</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>129</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="E53" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="F53" t="s">
-        <v>150</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>356</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>225</v>
       </c>
       <c r="E55" t="s">
-        <v>135</v>
+        <v>302</v>
       </c>
       <c r="F55" t="s">
-        <v>175</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="E56" t="s">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="F56" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>227</v>
       </c>
       <c r="E57" t="s">
-        <v>134</v>
+        <v>313</v>
       </c>
       <c r="F57" t="s">
-        <v>151</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>228</v>
       </c>
       <c r="E58" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>229</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F59" t="s">
-        <v>165</v>
+        <v>358</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="F60" t="s">
-        <v>163</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="E61" t="s">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="F61" t="s">
-        <v>176</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="E62" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="F62" t="s">
-        <v>153</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="E63" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F63" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="E64" t="s">
-        <v>138</v>
+        <v>307</v>
       </c>
       <c r="F64" t="s">
-        <v>166</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c r="E65" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="F65" t="s">
-        <v>163</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C66" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="F66" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="E67" t="s">
-        <v>130</v>
+        <v>309</v>
       </c>
       <c r="F67" t="s">
-        <v>163</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="E68" t="s">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="F68" t="s">
-        <v>158</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>105</v>
+        <v>239</v>
       </c>
       <c r="E69" t="s">
-        <v>139</v>
+        <v>313</v>
       </c>
       <c r="F69" t="s">
-        <v>167</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="E70" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="F70" t="s">
-        <v>153</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>241</v>
       </c>
       <c r="E71" t="s">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>364</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="D72" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="E72" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="F72" t="s">
-        <v>177</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>138</v>
+        <v>303</v>
       </c>
       <c r="F73" t="s">
-        <v>159</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="E74" t="s">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="F74" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="E75" t="s">
-        <v>130</v>
+        <v>309</v>
       </c>
       <c r="F75" t="s">
-        <v>168</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D76" t="s">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="E76" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="F76" t="s">
-        <v>153</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
       <c r="E77" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F77" t="s">
-        <v>178</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="D78" t="s">
-        <v>99</v>
+        <v>247</v>
       </c>
       <c r="E78" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="F78" t="s">
-        <v>161</v>
+        <v>351</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D79" t="s">
-        <v>114</v>
+        <v>248</v>
       </c>
       <c r="E79" t="s">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="F79" t="s">
-        <v>175</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="D80" t="s">
-        <v>86</v>
+        <v>249</v>
       </c>
       <c r="E80" t="s">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="F80" t="s">
-        <v>150</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>250</v>
       </c>
       <c r="E81" t="s">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="F81" t="s">
-        <v>169</v>
+        <v>331</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="E82" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F82" t="s">
-        <v>170</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
-        <v>121</v>
+        <v>251</v>
       </c>
       <c r="E83" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F83" t="s">
-        <v>179</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="D84" t="s">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="E84" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F84" t="s">
-        <v>176</v>
+        <v>370</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
-        <v>102</v>
+        <v>253</v>
       </c>
       <c r="E85" t="s">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="F85" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="D86" t="s">
-        <v>119</v>
+        <v>254</v>
       </c>
       <c r="E86" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F86" t="s">
-        <v>177</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>302</v>
       </c>
       <c r="F87" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="E88" t="s">
-        <v>140</v>
+        <v>308</v>
       </c>
       <c r="F88" t="s">
-        <v>145</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C89" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="E89" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F89" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="E90" t="s">
-        <v>137</v>
+        <v>312</v>
       </c>
       <c r="F90" t="s">
-        <v>156</v>
+        <v>372</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C91" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="D91" t="s">
-        <v>103</v>
+        <v>258</v>
       </c>
       <c r="E91" t="s">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="F91" t="s">
-        <v>165</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="E92" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="F92" t="s">
-        <v>180</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="B93" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="D93" t="s">
-        <v>123</v>
+        <v>260</v>
       </c>
       <c r="E93" t="s">
-        <v>140</v>
+        <v>308</v>
       </c>
       <c r="F93" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="E94" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F94" t="s">
-        <v>172</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C95" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="D95" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="E95" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F95" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="B96" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="C96" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="D96" t="s">
-        <v>95</v>
+        <v>263</v>
       </c>
       <c r="E96" t="s">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="F96" t="s">
-        <v>150</v>
+        <v>375</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C97" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="D97" t="s">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="E97" t="s">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="F97" t="s">
-        <v>166</v>
+        <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="B98" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
-        <v>124</v>
+        <v>265</v>
       </c>
       <c r="E98" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="F98" t="s">
-        <v>181</v>
+        <v>377</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="C99" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D99" t="s">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="E99" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="F99" t="s">
-        <v>145</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="D100" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="E100" t="s">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="F100" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C101" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="D101" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="E101" t="s">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="F101" t="s">
-        <v>160</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="E102" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F102" t="s">
-        <v>152</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>270</v>
       </c>
       <c r="E103" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="F103" t="s">
-        <v>163</v>
+        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="D104" t="s">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="E104" t="s">
-        <v>129</v>
+        <v>308</v>
       </c>
       <c r="F104" t="s">
-        <v>142</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="E105" t="s">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="F105" t="s">
-        <v>171</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="B106" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="D106" t="s">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="E106" t="s">
-        <v>129</v>
+        <v>311</v>
       </c>
       <c r="F106" t="s">
-        <v>144</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="B107" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="D107" t="s">
-        <v>125</v>
+        <v>274</v>
       </c>
       <c r="E107" t="s">
-        <v>130</v>
+        <v>312</v>
       </c>
       <c r="F107" t="s">
-        <v>147</v>
+        <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="D108" t="s">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="E108" t="s">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="F108" t="s">
-        <v>161</v>
+        <v>383</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B109" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
-        <v>126</v>
+        <v>276</v>
       </c>
       <c r="E109" t="s">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="F109" t="s">
-        <v>182</v>
+        <v>384</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>277</v>
       </c>
       <c r="E110" t="s">
-        <v>141</v>
+        <v>303</v>
       </c>
       <c r="F110" t="s">
-        <v>177</v>
+        <v>332</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D111" t="s">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="E111" t="s">
-        <v>130</v>
+        <v>312</v>
       </c>
       <c r="F111" t="s">
-        <v>147</v>
+        <v>317</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
       <c r="E112" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="F112" t="s">
-        <v>163</v>
+        <v>385</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="C113" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="D113" t="s">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="E113" t="s">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="F113" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="E114" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
+        <v>386</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="D115" t="s">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="E115" t="s">
-        <v>131</v>
+        <v>306</v>
       </c>
       <c r="F115" t="s">
-        <v>170</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C116" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="D116" t="s">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="E116" t="s">
-        <v>131</v>
+        <v>308</v>
       </c>
       <c r="F116" t="s">
-        <v>145</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="B117" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D117" t="s">
-        <v>127</v>
+        <v>284</v>
       </c>
       <c r="E117" t="s">
-        <v>141</v>
+        <v>307</v>
       </c>
       <c r="F117" t="s">
-        <v>177</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D118" t="s">
-        <v>128</v>
+        <v>285</v>
       </c>
       <c r="E118" t="s">
-        <v>129</v>
+        <v>307</v>
       </c>
       <c r="F118" t="s">
-        <v>183</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="B119" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="D119" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="E119" t="s">
-        <v>138</v>
+        <v>309</v>
       </c>
       <c r="F119" t="s">
-        <v>164</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="B120" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C120" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="D120" t="s">
-        <v>121</v>
+        <v>287</v>
       </c>
       <c r="E120" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="F120" t="s">
-        <v>180</v>
+        <v>316</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="B121" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="D121" t="s">
-        <v>125</v>
+        <v>288</v>
       </c>
       <c r="E121" t="s">
-        <v>130</v>
+        <v>309</v>
       </c>
       <c r="F121" t="s">
-        <v>147</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="C122" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="D122" t="s">
-        <v>92</v>
+        <v>289</v>
       </c>
       <c r="E122" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="F122" t="s">
-        <v>156</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D123" t="s">
-        <v>91</v>
+        <v>290</v>
       </c>
       <c r="E123" t="s">
-        <v>132</v>
+        <v>303</v>
       </c>
       <c r="F123" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="B124" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="D124" t="s">
-        <v>109</v>
+        <v>291</v>
       </c>
       <c r="E124" t="s">
-        <v>132</v>
+        <v>303</v>
       </c>
       <c r="F124" t="s">
-        <v>172</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="B125" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="D125" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="E125" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F125" t="s">
-        <v>172</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="C126" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="D126" t="s">
-        <v>124</v>
+        <v>293</v>
       </c>
       <c r="E126" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
-        <v>181</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C127" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="D127" t="s">
-        <v>90</v>
+        <v>294</v>
       </c>
       <c r="E127" t="s">
-        <v>136</v>
+        <v>312</v>
       </c>
       <c r="F127" t="s">
-        <v>154</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="B128" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="C128" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="D128" t="s">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="E128" t="s">
-        <v>138</v>
+        <v>307</v>
       </c>
       <c r="F128" t="s">
-        <v>166</v>
+        <v>337</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="B129" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="D129" t="s">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="E129" t="s">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="F129" t="s">
-        <v>150</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="B130" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="D130" t="s">
-        <v>123</v>
+        <v>297</v>
       </c>
       <c r="E130" t="s">
-        <v>140</v>
+        <v>313</v>
       </c>
       <c r="F130" t="s">
-        <v>171</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="B131" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C131" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>93</v>
+        <v>260</v>
       </c>
       <c r="E131" t="s">
-        <v>132</v>
+        <v>302</v>
       </c>
       <c r="F131" t="s">
-        <v>157</v>
+        <v>329</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="B132" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="C132" t="s">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="D132" t="s">
-        <v>85</v>
+        <v>298</v>
       </c>
       <c r="E132" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="F132" t="s">
-        <v>170</v>
+        <v>376</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="B133" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C133" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="D133" t="s">
-        <v>126</v>
+        <v>299</v>
       </c>
       <c r="E133" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="F133" t="s">
-        <v>182</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="C134" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="D134" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="E134" t="s">
-        <v>130</v>
+        <v>314</v>
       </c>
       <c r="F134" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135">
-        <v>133</v>
-      </c>
-      <c r="B135" t="s">
-        <v>32</v>
-      </c>
-      <c r="C135" t="s">
-        <v>68</v>
-      </c>
-      <c r="D135" t="s">
-        <v>105</v>
-      </c>
-      <c r="E135" t="s">
-        <v>139</v>
-      </c>
-      <c r="F135" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136">
-        <v>134</v>
-      </c>
-      <c r="B136" t="s">
-        <v>24</v>
-      </c>
-      <c r="C136" t="s">
-        <v>58</v>
-      </c>
-      <c r="D136" t="s">
-        <v>97</v>
-      </c>
-      <c r="E136" t="s">
-        <v>138</v>
-      </c>
-      <c r="F136" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>135</v>
-      </c>
-      <c r="B137" t="s">
-        <v>5</v>
-      </c>
-      <c r="C137" t="s">
-        <v>58</v>
-      </c>
-      <c r="D137" t="s">
-        <v>78</v>
-      </c>
-      <c r="E137" t="s">
-        <v>129</v>
-      </c>
-      <c r="F137" t="s">
-        <v>142</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
